--- a/results/tables/shap_importance.xlsx
+++ b/results/tables/shap_importance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,211 +443,211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>人口密度</t>
+          <t>Load_lag_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.4816337082886</v>
+        <v>304.9304727413622</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>车流量</t>
+          <t>Load_lag_24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.68358142030505</v>
+        <v>46.24569017505152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>是否工作日</t>
+          <t>人口密度</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56.903081974944</v>
+        <v>23.31469681263346</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>小时_3</t>
+          <t>小时_7</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.82518390550013</v>
+        <v>16.66509415289043</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>小时_23</t>
+          <t>小时_17</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.44094264580485</v>
+        <v>15.02958055045046</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>小时_16</t>
+          <t>是否工作日</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.01444862855455</v>
+        <v>12.41151849656547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>小时_0</t>
+          <t>车流量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.73820670235535</v>
+        <v>7.821022893561102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>小时_15</t>
+          <t>小时_11</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.96638867887475</v>
+        <v>7.582240433914104</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>小时_13</t>
+          <t>小时_10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.74667583315407</v>
+        <v>6.364815842898297</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>小时_11</t>
+          <t>小时_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20.69693406339712</v>
+        <v>6.256510703832229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>小时_1</t>
+          <t>小时_21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.48839196501494</v>
+        <v>5.585042660933461</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>区域总面积</t>
+          <t>小时_6</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.43403908970687</v>
+        <v>4.771397882909772</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>小时_4</t>
+          <t>小时_22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.83044709014197</v>
+        <v>4.087634917552166</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>电网容量</t>
+          <t>区域类型_城市新区</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.91653435722679</v>
+        <v>3.36838233680307</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>小时_17</t>
+          <t>小时_8</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.68355090143922</v>
+        <v>2.870858501919355</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>小时_5</t>
+          <t>小时_4</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15.6214770876071</v>
+        <v>2.491161613335119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>小时_2</t>
+          <t>小时_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.5701346962923</v>
+        <v>2.414431299893063</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>小时_19</t>
+          <t>小时_12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11.80476126002621</v>
+        <v>2.194402610562558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>小时_12</t>
+          <t>区域总面积</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11.47818488347967</v>
+        <v>2.131314467233798</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>小时_14</t>
+          <t>电网容量</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.723661022084041</v>
+        <v>2.120410618682959</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>小时_10</t>
+          <t>小时_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.649652257501504</v>
+        <v>2.069144887441309</v>
       </c>
     </row>
     <row r="23">
@@ -657,117 +657,167 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.0828529826644</v>
+        <v>2.005128468634808</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>充电桩数量</t>
+          <t>小时_13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6.388258071151272</v>
+        <v>1.935242125646226</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>小时_21</t>
+          <t>小时_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.398121807259158</v>
+        <v>1.868182304673306</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>小时_6</t>
+          <t>小时_19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.342404193528896</v>
+        <v>1.244054623047051</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>小时_22</t>
+          <t>小时_2</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.904943395285147</v>
+        <v>1.030680906200107</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>小时_20</t>
+          <t>小时_23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.145569355259415</v>
+        <v>0.8558266831062931</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>小时_8</t>
+          <t>小时_1</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.712737693557634</v>
+        <v>0.7628046315365501</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>慢充数量</t>
+          <t>充电桩数量</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.549641055228496</v>
+        <v>0.7605826507498139</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>小时_9</t>
+          <t>小时_3</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.508137696066656</v>
+        <v>0.7316054923685665</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>快充数量</t>
+          <t>小时_14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.408909823919333</v>
+        <v>0.6963745683436219</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>小时_7</t>
+          <t>商业POI数</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.369110135778315</v>
+        <v>0.640233004047788</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>商业POI数</t>
+          <t>小时_15</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.323741755911191</v>
+        <v>0.5086317712018806</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>快充数量</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.2249394323000904</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>小时_0</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.1920255911458703</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>区域类型_城郊工业区</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.09009788702033869</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>慢充数量</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.07781755980880863</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>区域类型_老城核心区</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.07688137863127578</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/shap_importance.xlsx
+++ b/results/tables/shap_importance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,381 +443,281 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Load_lag_1</t>
+          <t>period_凌晨</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>304.9304727413622</v>
+        <v>0.581323356630121</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Load_lag_24</t>
+          <t>hour_cos</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46.24569017505152</v>
+        <v>0.5246318806931032</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>人口密度</t>
+          <t>hour_sin</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.31469681263346</v>
+        <v>0.4121125740032408</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>小时_7</t>
+          <t>region_load_prior</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.66509415289043</v>
+        <v>0.2100209513156397</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>小时_17</t>
+          <t>是否工作日</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.02958055045046</v>
+        <v>0.1025988800820482</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>是否工作日</t>
+          <t>车流量</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.41151849656547</v>
+        <v>0.05984550836158925</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>车流量</t>
+          <t>设施供给强度</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.821022893561102</v>
+        <v>0.03983851176731534</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>小时_11</t>
+          <t>period_上午</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.582240433914104</v>
+        <v>0.0365767669516766</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>小时_10</t>
+          <t>period_夜间</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.364815842898297</v>
+        <v>0.03589746272723567</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>小时_9</t>
+          <t>人口密度</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.256510703832229</v>
+        <v>0.03482263035061501</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>小时_21</t>
+          <t>period_下午</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.585042660933461</v>
+        <v>0.0245469765930898</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>小时_6</t>
+          <t>电网容量</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.771397882909772</v>
+        <v>0.01344435370189742</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>小时_22</t>
+          <t>充电桩数量</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.087634917552166</v>
+        <v>0.01310783960346539</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>区域类型_城市新区</t>
+          <t>区域总面积</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.36838233680307</v>
+        <v>0.01159894087506113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>小时_8</t>
+          <t>充电桩密度</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.870858501919355</v>
+        <v>0.008874444337682584</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>小时_4</t>
+          <t>商业POI数</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.491161613335119</v>
+        <v>0.007630456713005609</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>小时_16</t>
+          <t>充电覆盖面积</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.414431299893063</v>
+        <v>0.007593071425654673</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>小时_12</t>
+          <t>交通强度</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.194402610562558</v>
+        <v>0.006497639855327313</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>区域总面积</t>
+          <t>peak_morning</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.131314467233798</v>
+        <v>0.004231078329994225</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>电网容量</t>
+          <t>商业密度</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.120410618682959</v>
+        <v>0.003865199172321442</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>小时_20</t>
+          <t>区域类型_城市新区</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.069144887441309</v>
+        <v>0.003485904271355891</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>小时_18</t>
+          <t>慢充数量</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.005128468634808</v>
+        <v>0.003436604492671514</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>小时_13</t>
+          <t>快充数量</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.935242125646226</v>
+        <v>0.003339787524009897</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>小时_5</t>
+          <t>快充比例</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.868182304673306</v>
+        <v>0.003229664965077303</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>小时_19</t>
+          <t>区域类型_城郊工业区</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.244054623047051</v>
+        <v>0.002829651643632465</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>小时_2</t>
+          <t>区域类型_老城核心区</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.030680906200107</v>
+        <v>0.00180448584730101</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>小时_23</t>
+          <t>peak_evening</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8558266831062931</v>
+        <v>0.001501701877155105</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>小时_1</t>
+          <t>period_晚高峰</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7628046315365501</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>充电桩数量</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0.7605826507498139</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>小时_3</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0.7316054923685665</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>小时_14</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0.6963745683436219</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>商业POI数</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0.640233004047788</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>小时_15</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0.5086317712018806</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>快充数量</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0.2249394323000904</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>小时_0</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0.1920255911458703</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>区域类型_城郊工业区</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0.09009788702033869</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>慢充数量</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0.07781755980880863</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>区域类型_老城核心区</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.07688137863127578</v>
+        <v>0.0001725864918245411</v>
       </c>
     </row>
   </sheetData>
